--- a/AAII_Financials/Yearly/RDNT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RDNT_YR_FIN.xlsx
@@ -4099,7 +4099,7 @@
         <v>177300</v>
       </c>
       <c r="G83" s="3">
-        <v>174600</v>
+        <v>105800</v>
       </c>
       <c r="H83" s="3">
         <v>166300</v>
